--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20211.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -79,58 +79,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>GASPAR</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
   </si>
   <si>
     <t>KEVIN ISAAC</t>
@@ -139,28 +136,10 @@
     <t>EDGAR FLORENCIO</t>
   </si>
   <si>
-    <t>YAIR</t>
+    <t>MARIA VALERIA</t>
   </si>
   <si>
     <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IKER XAVIER</t>
   </si>
 </sst>
 </file>
@@ -561,19 +540,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>62.5</v>
+        <v>72.5</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -587,19 +566,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>70.45</v>
+        <v>79.55</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -613,16 +592,16 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4">
-        <v>86.05</v>
+        <v>90.7</v>
       </c>
       <c r="H4">
         <v>6.6</v>
@@ -639,19 +618,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>75.86</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -665,19 +644,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>61.9</v>
+        <v>76.19</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -730,16 +709,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>72.5</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -753,16 +735,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>77.27</v>
+      </c>
+      <c r="H3">
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -776,16 +761,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -799,16 +787,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>65.52</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -822,16 +813,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H6">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -884,19 +878,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>62.5</v>
+        <v>72.5</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -910,19 +904,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>70.45</v>
+        <v>79.55</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -936,19 +930,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4">
-        <v>86.05</v>
+        <v>90.7</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -962,19 +956,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>75.86</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -988,19 +982,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>61.9</v>
+        <v>76.19</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,16 +1036,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>21330051920017</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1060,159 +1054,159 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920006</v>
+        <v>21330051920067</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920017</v>
+        <v>21330051920078</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920379</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920067</v>
+        <v>21330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920078</v>
+        <v>21330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920101</v>
+        <v>21330051920355</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920355</v>
+        <v>21330051920379</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1221,52 +1215,6 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920126</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920275</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20211.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -79,64 +79,70 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
     <t>YAIR</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
   </si>
   <si>
     <t>MIGUEL</t>
@@ -1004,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1036,22 +1042,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920017</v>
+        <v>21330051920043</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1065,10 +1071,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1077,7 +1083,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1088,10 +1094,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1114,7 +1120,7 @@
         <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1137,7 +1143,7 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1160,7 +1166,7 @@
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1169,7 +1175,7 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1183,7 +1189,7 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1197,7 +1203,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920379</v>
+        <v>21330051920017</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
@@ -1206,7 +1212,7 @@
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1215,6 +1221,29 @@
         <v>9</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920379</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20211.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="99">
   <si>
     <t>Mat</t>
   </si>
@@ -79,73 +79,241 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MOSTRANZO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZALAVA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RIVADENEYRA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>CARLOS URIEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>THANIA CRISTAL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>JOSIAH</t>
+  </si>
+  <si>
+    <t>OLIVER ULISES</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>EBER</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
   </si>
   <si>
     <t>HANIA ZARETH</t>
   </si>
   <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
     <t>MIROSLAVA</t>
   </si>
   <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
+    <t>FATIMA MARILYN</t>
   </si>
 </sst>
 </file>
@@ -546,19 +714,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -572,19 +740,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>79.55</v>
+        <v>86.36</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -598,19 +766,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>90.7</v>
+        <v>93.02</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -624,19 +792,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>82.76000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -650,19 +818,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -715,19 +883,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -741,19 +909,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>77.27</v>
+        <v>86.36</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -767,19 +935,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>79.06999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -793,19 +961,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>65.52</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -819,19 +987,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -884,19 +1052,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>72.5</v>
+        <v>67.5</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -910,19 +1078,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>79.55</v>
+        <v>86.36</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -936,19 +1104,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>90.7</v>
+        <v>88.37</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -962,19 +1130,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>82.76000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -988,19 +1156,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,16 +1210,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920043</v>
+        <v>21330051920388</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1065,16 +1233,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920067</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1088,16 +1256,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920078</v>
+        <v>21330051920108</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1106,21 +1274,21 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920120</v>
+        <v>21330051920110</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1129,27 +1297,27 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920005</v>
+        <v>21330051920120</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1157,45 +1325,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920006</v>
+        <v>21330051920128</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920355</v>
+        <v>21330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1203,48 +1371,531 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920017</v>
+        <v>21330051920144</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920379</v>
+        <v>21330051920384</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920395</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920147</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920002</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920006</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920380</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920355</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920018</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920013</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920017</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920379</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920385</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920020</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920024</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920025</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920393</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920057</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920061</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920067</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920069</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920078</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920089</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
